--- a/artfynd/A 62805-2025 artfynd.xlsx
+++ b/artfynd/A 62805-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130754902</v>
       </c>
       <c r="B2" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130756304</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>130756077</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62805-2025 artfynd.xlsx
+++ b/artfynd/A 62805-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130754902</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130756304</v>
       </c>
       <c r="B3" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>130756077</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62805-2025 artfynd.xlsx
+++ b/artfynd/A 62805-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130754902</v>
       </c>
       <c r="B2" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130756304</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>130756077</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62805-2025 artfynd.xlsx
+++ b/artfynd/A 62805-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130754902</v>
+        <v>130756077</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481082</v>
+        <v>481469</v>
       </c>
       <c r="R2" t="n">
-        <v>6541732</v>
+        <v>6541470</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +780,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,11 +820,11 @@
         <v>130756304</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -934,27 +959,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130756077</v>
+        <v>108291008</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,24 +988,25 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klämmabäcken, Klämmabäcken, Nrk</t>
+          <t>Klämmabäcken, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481469</v>
+        <v>481079</v>
       </c>
       <c r="R4" t="n">
-        <v>6541470</v>
+        <v>6541607</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,27 +1030,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska hack i död tall</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,44 +1056,366 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108291138</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klämmabäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>481018</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6541763</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130754902</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Klämmabäcken, Klämmabäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>481082</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6541732</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Per Arneborn</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Per Arneborn</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108290962</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klämmabäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>481076</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6541603</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62805-2025 artfynd.xlsx
+++ b/artfynd/A 62805-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108291138</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -931,6 +941,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130756077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1073,6 +1088,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130756304</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1186,6 +1206,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108291008</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1303,6 +1328,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754902</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1416,8 +1446,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108290962</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>